--- a/data/price_audit.xlsx
+++ b/data/price_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ревизия цен" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как считано" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Общие расходы Ozon" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ревизия цен" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Как считано" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Общие расходы Ozon" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ревизия цен'!$A$1:$O$124</definedName>
@@ -78,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -93,6 +93,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -558,50 +559,52 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>600</v>
+        <v>1900</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1950</v>
+        <v>6850</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>710</v>
+        <v>-465</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 1 продаж</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-7</v>
+        <v>-2776</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-0.00358974358974359</v>
+        <v>-0.4053124087591241</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1370</v>
+        <v>4800</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>619</v>
+        <v>2372</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1370</v>
+        <v>6220</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>647</v>
-      </c>
-      <c r="N2" s="2" t="n"/>
+        <v>3760</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
@@ -611,498 +614,516 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
+          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>490</v>
+        <v>4850</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>76</v>
+        <v>-6916</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 1 продаж</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-34</v>
+        <v>-7807</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-0.0685714285714286</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>340</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>223</v>
-      </c>
+        <v>-1.609719587628866</v>
+      </c>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n">
-        <v>340</v>
+        <v>3320</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="N3" s="2" t="n"/>
+        <v>2421</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>УБЫТОК Ozon</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>0am325025j</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>-197</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>факт: 4 продаж</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-618</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>-0.216809649122807</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1521</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1588</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-2050</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>факт: 3 продаж</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-2371</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>-0.8317707602339182</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>1621</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>1670</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>123014‑AF</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>факт: 4 продаж</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-52</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>-0.03825925925925926</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>737</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1040</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>846</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>01X301127C</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X301127C</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-82</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>факт: 8 продаж</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-234</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>-0.2468197368421053</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>670</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>501</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>620</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>469</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>0cw0amdsgdq200</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-216</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>факт: 3 продаж</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-303</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>-0.3188456140350877</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>670</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>566</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>516</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>WHT001922</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-27</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>факт: 24 продаж</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-179</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>-0.1884820175438597</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>670</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>501</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>690</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>533</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-dq200</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2 кольца-прокладки на 1 втулку мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>факт: 1 продаж</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>-54</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>-0.05668421052631579</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>670</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>546</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>590</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>487</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>490</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-54</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>-0.1093877551020409</v>
-      </c>
-      <c r="J4" s="3" t="n">
+      <c r="E11" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>факт: 5 продаж</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>-0.004168421052631557</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>670</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>496</v>
+      </c>
+      <c r="L11" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>340</v>
-      </c>
-      <c r="M4" s="3" t="n">
+      <c r="M11" s="3" t="n">
         <v>209</v>
       </c>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="N11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>УБЫТОК Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>02E927770AL</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>118000</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>60242</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>13162</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>0.1115423728813559</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>70800</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>23012</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>70800</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>24428</v>
-      </c>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>0am325025x</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>78475</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>35994</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>16286</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.207524689391526</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>47090</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>26910</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>47090</v>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>27852</v>
-      </c>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>0am325025H</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG7 DQ200 0AM/0CW ПРОВЕРЕН НА АВТО</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>13000</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>68800</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>30963</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>13835</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>0.2010901162790698</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>41280</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>23739</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>41280</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>24565</v>
-      </c>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>58900</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>27914</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>14380</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0.2441426146010187</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>35340</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>21453</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>35340</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>22159</v>
-      </c>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>6t30</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>19800</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>10069</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1881</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n">
-        <v>13860</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>5613</v>
-      </c>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>низкая маржа Ozon</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>0am325025</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>3400</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>12890</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>6222</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>2048</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.1589138867339024</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>9020</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>4628</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>9020</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>4808</v>
-      </c>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>0AM325587E</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал VAG 0AM325587E</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>9850</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>4895</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>2504</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>0.2542131979695432</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>6900</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>4341</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>6900</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>4479</v>
-      </c>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2100</v>
+        <v>30500</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>9500</v>
+        <v>118850</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>4636</v>
+        <v>60684</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -1110,24 +1131,26 @@
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1966</v>
+        <v>23053</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2069473684210526</v>
+        <v>0.1939671855279765</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>6650</v>
+        <v>71310</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>3818</v>
+        <v>32966</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>6650</v>
+        <v>70800</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>3951</v>
-      </c>
-      <c r="N12" s="5" t="n"/>
+        <v>33928</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -1137,103 +1160,107 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769D</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1400</v>
+        <v>31000</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9479</v>
+        <v>118850</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4750</v>
+        <v>42266</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 2 продаж</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2781</v>
+        <v>4135</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.2934212469669796</v>
+        <v>0.03479444678165755</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>6640</v>
+        <v>71310</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>4510</v>
+        <v>32466</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>6640</v>
+        <v>77280</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>4642</v>
-      </c>
-      <c r="N13" s="5" t="n"/>
+        <v>39325</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1400</v>
+        <v>15000</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>8979</v>
+        <v>78850</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>4490</v>
+        <v>37568</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 2 продаж</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2551</v>
+        <v>17837</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2841452277536474</v>
+        <v>0.2262175649968294</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>6290</v>
+        <v>47310</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>4198</v>
+        <v>27106</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>6290</v>
+        <v>47090</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>4324</v>
-      </c>
-      <c r="N14" s="5" t="n"/>
+        <v>27852</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -1243,131 +1270,135 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1000</v>
+        <v>17500</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>8900</v>
+        <v>74850</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>4449</v>
+        <v>22451</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 3 продаж</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2915</v>
+        <v>460</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.3275280898876404</v>
+        <v>0.006147227788911142</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>6230</v>
+        <v>44910</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>4545</v>
+        <v>22470</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>6230</v>
+        <v>47280</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>4669</v>
-      </c>
-      <c r="N15" s="5" t="n"/>
+        <v>25525</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
+          <t>Мехатроник DSG7 DQ200 0AM/0CW ПРОВЕРЕН НА АВТО</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1800</v>
+        <v>13800</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>8890</v>
+        <v>68850</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4396</v>
+        <v>28084</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 7 продаж</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2062</v>
+        <v>10153</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.2319910011248594</v>
+        <v>0.1474629318394025</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>6220</v>
+        <v>41310</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>3736</v>
+        <v>22966</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>6220</v>
+        <v>41280</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>3860</v>
-      </c>
-      <c r="N16" s="5" t="n"/>
+        <v>23765</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>161</v>
+        <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>700</v>
+        <v>10000</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>8879</v>
+        <v>58850</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4313</v>
+        <v>27888</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
@@ -1375,22 +1406,22 @@
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3080</v>
+        <v>14357</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.3469242031760333</v>
+        <v>0.2439592183517417</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>6220</v>
+        <v>35310</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>4836</v>
+        <v>21426</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>6220</v>
+        <v>35340</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>4960</v>
+        <v>22159</v>
       </c>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="inlineStr">
@@ -1402,103 +1433,107 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1900</v>
+        <v>3000</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>8879</v>
+        <v>12850</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>4313</v>
+        <v>5675</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 31 продаж</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
-        <v>1880</v>
+        <v>1904</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.2117738484063521</v>
+        <v>0.148188326848249</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>6220</v>
+        <v>9000</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>3636</v>
+        <v>5010</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>6220</v>
+        <v>9020</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>3760</v>
-      </c>
-      <c r="N18" s="5" t="n"/>
+        <v>5208</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>31</v>
+      </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал VAG 0AM325587E</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>8850</v>
+        <v>9850</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>4423</v>
+        <v>4683</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 18 продаж</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2892</v>
+        <v>2292</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0.3267796610169492</v>
+        <v>0.2327241962774957</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>6200</v>
+        <v>6900</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>4518</v>
+        <v>4341</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>6200</v>
+        <v>6900</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>4642</v>
-      </c>
-      <c r="N19" s="5" t="n"/>
+        <v>4479</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -1508,25 +1543,25 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>8850</v>
+        <v>9850</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4398</v>
+        <v>4818</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
@@ -1534,22 +1569,22 @@
         </is>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2867</v>
+        <v>2127</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.323954802259887</v>
+        <v>0.2159390862944162</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>6200</v>
+        <v>6900</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>4518</v>
+        <v>4041</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>6200</v>
+        <v>6650</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>4642</v>
+        <v>3951</v>
       </c>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="inlineStr">
@@ -1561,127 +1596,135 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2000</v>
+        <v>1400</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>8500</v>
+        <v>9350</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4116</v>
+        <v>3725</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 3 продаж</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1606</v>
+        <v>1764</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.1889411764705882</v>
+        <v>0.1886695187165775</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>5950</v>
+        <v>6550</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>3295</v>
+        <v>4429</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>5950</v>
+        <v>6640</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>3414</v>
-      </c>
-      <c r="N21" s="5" t="n"/>
+        <v>4642</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%; комплект дешевле детали 0am325066ae (8879)</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2100</v>
+        <v>700</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>8500</v>
+        <v>8850</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4116</v>
+        <v>4341</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 6 продаж</t>
         </is>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1506</v>
+        <v>3110</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.1771764705882353</v>
-      </c>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
+        <v>0.3513998116760829</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>4818</v>
+      </c>
       <c r="L22" s="6" t="n">
-        <v>5950</v>
+        <v>6220</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>3314</v>
-      </c>
-      <c r="N22" s="5" t="n"/>
+        <v>4960</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>комплект дешевле детали 0am325066ae (8879)</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>8500</v>
+        <v>8850</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4116</v>
+        <v>4423</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
@@ -1689,120 +1732,134 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1506</v>
+        <v>2492</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.1771764705882353</v>
+        <v>0.2815819209039548</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>5950</v>
+        <v>6200</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>3195</v>
+        <v>4118</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>5950</v>
+        <v>6290</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>3314</v>
+        <v>4324</v>
       </c>
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%; комплект дешевле детали 0am325066ae (8879)</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1900</v>
+        <v>1000</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="7" t="n"/>
+        <v>8850</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>4295</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>факт: 3 продаж</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>2764</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.3123578154425612</v>
+      </c>
       <c r="J24" s="6" t="n">
-        <v>5950</v>
+        <v>6200</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>3395</v>
+        <v>4518</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>5950</v>
+        <v>6200</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>3514</v>
-      </c>
-      <c r="N24" s="5" t="n"/>
+        <v>4642</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>комплект дешевле детали 0am325066ae (8879)</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>1000</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>7979</v>
+        <v>8850</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>3945</v>
+        <v>4295</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 5 продаж</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2466</v>
+        <v>2764</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.3091038977315453</v>
+        <v>0.3123593220338983</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>5590</v>
+        <v>6200</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>3975</v>
+        <v>4518</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>5590</v>
+        <v>6200</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>4087</v>
-      </c>
-      <c r="N25" s="5" t="n"/>
+        <v>4642</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -1812,25 +1869,25 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>7979</v>
+        <v>8850</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>3945</v>
+        <v>4375</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
@@ -1838,22 +1895,22 @@
         </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2466</v>
+        <v>2044</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.3091038977315453</v>
+        <v>0.2309604519774011</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>5590</v>
+        <v>6200</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>3975</v>
+        <v>3718</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>5590</v>
+        <v>6220</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>4087</v>
+        <v>3860</v>
       </c>
       <c r="N26" s="5" t="n"/>
       <c r="O26" s="5" t="inlineStr">
@@ -1865,12 +1922,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -1880,53 +1937,63 @@
         <v>2000</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="7" t="n"/>
+        <v>8850</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>4298</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1767</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.1996610169491525</v>
+      </c>
       <c r="J27" s="6" t="n">
-        <v>5250</v>
+        <v>6200</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>2672</v>
+        <v>3518</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>5250</v>
+        <v>5950</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>2778</v>
+        <v>3414</v>
       </c>
       <c r="N27" s="5" t="n"/>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>дубль с другой ценой: plita-filtr-v2; комплект дешевле детали 0am325066ae (8879)</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>2100</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>7500</v>
+        <v>8850</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3596</v>
+        <v>4298</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
@@ -1934,52 +2001,54 @@
         </is>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1046</v>
+        <v>1667</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>0.1394666666666667</v>
+        <v>0.188361581920904</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>5250</v>
+        <v>6200</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>2572</v>
+        <v>3418</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>5250</v>
+        <v>5950</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>2678</v>
-      </c>
-      <c r="N28" s="5" t="n"/>
+        <v>3314</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%; комплект дешевле детали 0am325066ae (8879)</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>7500</v>
+        <v>8850</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3596</v>
+        <v>4298</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
@@ -1987,77 +2056,79 @@
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1146</v>
+        <v>1867</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.1528</v>
+        <v>0.2109604519774011</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5850</v>
+        <v>6200</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>3206</v>
+        <v>3618</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>5850</v>
+        <v>5950</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>3323</v>
+        <v>3514</v>
       </c>
       <c r="N29" s="5" t="n"/>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%; дубль с другой ценой: plita-filtr; комплект дешевле детали 0am325066ae (8879)</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>7400</v>
+        <v>8850</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>3669</v>
+        <v>4465</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 2 продаж</t>
         </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1925</v>
+        <v>2934</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.2601351351351351</v>
+        <v>0.3315768361581921</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>5180</v>
+        <v>6200</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>3310</v>
+        <v>4518</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>5180</v>
+        <v>6230</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>3414</v>
-      </c>
-      <c r="N30" s="5" t="n"/>
+        <v>4669</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -2067,25 +2138,25 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>6050</v>
+        <v>7850</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2857</v>
+        <v>3878</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -2093,24 +2164,26 @@
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1594</v>
+        <v>2407</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.2634710743801653</v>
+        <v>0.3066242038216561</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>4240</v>
+        <v>5500</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>2874</v>
+        <v>3895</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>4240</v>
+        <v>5590</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>2958</v>
-      </c>
-      <c r="N31" s="5" t="n"/>
+        <v>4087</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -2120,25 +2193,25 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>5879</v>
+        <v>7850</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2853</v>
+        <v>3878</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
@@ -2146,22 +2219,22 @@
         </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1600</v>
+        <v>2407</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>0.2722129613879912</v>
+        <v>0.3066242038216561</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>4120</v>
+        <v>5500</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>2767</v>
+        <v>3895</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>4120</v>
+        <v>5590</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>2849</v>
+        <v>4087</v>
       </c>
       <c r="N32" s="5" t="n"/>
       <c r="O32" s="5" t="inlineStr">
@@ -2173,62 +2246,68 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D33" s="6" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>2000</v>
+      </c>
       <c r="E33" s="6" t="n">
-        <v>5700</v>
+        <v>7850</v>
       </c>
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="6" t="n">
-        <v>3990</v>
-      </c>
-      <c r="K33" s="6" t="n"/>
+        <v>5500</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>2895</v>
+      </c>
       <c r="L33" s="6" t="n">
-        <v>3990</v>
-      </c>
-      <c r="M33" s="6" t="n"/>
+        <v>5250</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>2778</v>
+      </c>
       <c r="N33" s="5" t="n"/>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>нет закупки</t>
+          <t>дубль с другой ценой: plita-filtr-v2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>600</v>
+        <v>2100</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>4990</v>
+        <v>7850</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>2416</v>
+        <v>3778</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -2236,22 +2315,22 @@
         </is>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1516</v>
+        <v>1207</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>0.3038877755511022</v>
+        <v>0.1537579617834395</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3490</v>
+        <v>5500</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2506</v>
+        <v>2795</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>3490</v>
+        <v>5250</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>2576</v>
+        <v>2678</v>
       </c>
       <c r="N34" s="5" t="n"/>
       <c r="O34" s="5" t="inlineStr">
@@ -2263,25 +2342,25 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>151</v>
+        <v>45</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>4490</v>
+        <v>7850</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2156</v>
+        <v>3778</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
@@ -2289,77 +2368,81 @@
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1086</v>
+        <v>1307</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>0.2419599109131403</v>
+        <v>0.1664968152866242</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>3140</v>
+        <v>5850</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1995</v>
+        <v>3206</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>3140</v>
+        <v>5850</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>2057</v>
-      </c>
-      <c r="N35" s="5" t="n"/>
+        <v>3323</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%; дубль с другой ценой: plita-filtr</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>4490</v>
+        <v>7350</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>2156</v>
+        <v>3840</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 1 продаж</t>
         </is>
       </c>
       <c r="H36" s="6" t="n">
-        <v>986</v>
+        <v>2099</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>0.2196881959910913</v>
+        <v>0.285578231292517</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>3140</v>
+        <v>5150</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>1895</v>
+        <v>3283</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>3140</v>
+        <v>5180</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>1957</v>
-      </c>
-      <c r="N36" s="5" t="n"/>
+        <v>3414</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -2369,244 +2452,252 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>4130</v>
+        <v>6350</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1944</v>
+        <v>1925</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 4 продаж</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1196</v>
+        <v>844</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>0.2895399515738499</v>
+        <v>0.1328877952755906</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>2890</v>
+        <v>4450</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>2072</v>
+        <v>3260</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>2890</v>
+        <v>4240</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>2130</v>
-      </c>
-      <c r="N37" s="5" t="n"/>
+        <v>3158</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>500</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="n">
-        <v>3879</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>1813</v>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>0.2785099252384635</v>
-      </c>
+        <v>5850</v>
+      </c>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="7" t="n"/>
       <c r="J38" s="6" t="n">
-        <v>2720</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>1921</v>
-      </c>
+        <v>4090</v>
+      </c>
+      <c r="K38" s="6" t="n"/>
       <c r="L38" s="6" t="n">
-        <v>2720</v>
-      </c>
-      <c r="M38" s="6" t="n">
-        <v>1975</v>
-      </c>
+        <v>3990</v>
+      </c>
+      <c r="M38" s="6" t="n"/>
       <c r="N38" s="5" t="n"/>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>нет закупки</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="6" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>500</v>
+      </c>
       <c r="E39" s="6" t="n">
-        <v>3879</v>
-      </c>
-      <c r="F39" s="6" t="n"/>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="6" t="n"/>
-      <c r="I39" s="7" t="n"/>
-      <c r="J39" s="6" t="n"/>
-      <c r="K39" s="6" t="n"/>
+        <v>5350</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>2573</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>1752</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>0.3274766355140187</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>4090</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>3140</v>
+      </c>
       <c r="L39" s="6" t="n">
-        <v>2720</v>
-      </c>
-      <c r="M39" s="6" t="n"/>
+        <v>4120</v>
+      </c>
+      <c r="M39" s="6" t="n">
+        <v>3249</v>
+      </c>
       <c r="N39" s="5" t="n"/>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>нет закупки</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>3879</v>
+        <v>4850</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1838</v>
+        <v>1883</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 1 продаж</t>
         </is>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1405</v>
+        <v>1092</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>0.3622944057746842</v>
+        <v>0.2251938144329897</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>2720</v>
+        <v>2700</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>2221</v>
+        <v>1903</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>2720</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>2275</v>
-      </c>
-      <c r="N40" s="5" t="n"/>
+        <v>1975</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%; дубль с другой ценой: Dq500</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>3879</v>
+        <v>4850</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1838</v>
+        <v>2423</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 5 продаж</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1205</v>
+        <v>1532</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>0.3107347254447022</v>
+        <v>0.3157760824742268</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>2720</v>
+        <v>3400</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>2021</v>
+        <v>2426</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>2720</v>
+        <v>3490</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>2075</v>
-      </c>
-      <c r="N41" s="5" t="n"/>
+        <v>2576</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -2616,174 +2707,190 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>3879</v>
+        <v>4350</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1838</v>
+        <v>1438</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 2 продаж</t>
         </is>
       </c>
       <c r="H42" s="6" t="n">
-        <v>1256</v>
+        <v>677</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>0.3236994070636762</v>
+        <v>0.1555632183908046</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>2720</v>
+        <v>3050</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>2071</v>
+        <v>2214</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>2720</v>
+        <v>2890</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>2125</v>
-      </c>
-      <c r="N42" s="5" t="n"/>
+        <v>2130</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%; дубль с другой ценой: DQ500</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D43" s="6" t="n"/>
+        <v>151</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>800</v>
+      </c>
       <c r="E43" s="6" t="n">
-        <v>3879</v>
+        <v>4350</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1813</v>
+        <v>2020</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="n"/>
-      <c r="I43" s="7" t="n"/>
+          <t>факт: 4 продаж</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>959</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>0.2205655172413793</v>
+      </c>
       <c r="J43" s="6" t="n">
-        <v>2720</v>
-      </c>
-      <c r="K43" s="6" t="n"/>
+        <v>3050</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>1914</v>
+      </c>
       <c r="L43" s="6" t="n">
-        <v>2720</v>
-      </c>
-      <c r="M43" s="6" t="n"/>
-      <c r="N43" s="5" t="n"/>
+        <v>3140</v>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>2057</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>нет закупки</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>3850</v>
+        <v>4350</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1823</v>
+        <v>1325</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 13 продаж</t>
         </is>
       </c>
       <c r="H44" s="6" t="n">
-        <v>1092</v>
+        <v>164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>0.2836363636363636</v>
+        <v>0.0377319186560566</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>2720</v>
+        <v>3050</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>1921</v>
+        <v>1814</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>2720</v>
+        <v>3140</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>1975</v>
-      </c>
-      <c r="N44" s="5" t="n"/>
+        <v>1957</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%; дубль с другой ценой: Dq500</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>229</v>
+        <v>23</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>3620</v>
+        <v>3850</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1703</v>
+        <v>1798</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -2791,24 +2898,26 @@
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1086</v>
+        <v>1217</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>0.3000552486187845</v>
+        <v>0.3161038961038961</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>2530</v>
+        <v>2700</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>1852</v>
+        <v>2053</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>2530</v>
+        <v>2720</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>1902</v>
-      </c>
-      <c r="N45" s="5" t="n"/>
+        <v>2125</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -2818,50 +2927,52 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>177</v>
+        <v>61</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>3479</v>
+        <v>3850</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1630</v>
+        <v>1830</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 7 продаж</t>
         </is>
       </c>
       <c r="H46" s="6" t="n">
-        <v>1171</v>
+        <v>1399</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>0.3366887036504743</v>
+        <v>0.363447866419295</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>2440</v>
+        <v>2700</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>1922</v>
+        <v>2203</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>2440</v>
+        <v>2720</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>1970</v>
-      </c>
-      <c r="N46" s="5" t="n"/>
+        <v>2275</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -2871,50 +2982,52 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>400</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>2890</v>
+        <v>3850</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1324</v>
+        <v>1844</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 11 продаж</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>750</v>
+        <v>1213</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>0.2596539792387543</v>
+        <v>0.3151072018890201</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>2020</v>
+        <v>2700</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>1398</v>
+        <v>2003</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>2020</v>
+        <v>2720</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>1438</v>
-      </c>
-      <c r="N47" s="5" t="n"/>
+        <v>2075</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -2924,131 +3037,135 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>5</v>
+        <v>229</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>2890</v>
+        <v>3850</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1276</v>
+        <v>1124</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 3 продаж</t>
         </is>
       </c>
       <c r="H48" s="6" t="n">
-        <v>602</v>
+        <v>493</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>0.2084429065743944</v>
+        <v>0.1280545454545454</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>2020</v>
+        <v>2700</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>1298</v>
+        <v>2003</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>2020</v>
+        <v>2530</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>1338</v>
-      </c>
-      <c r="N48" s="5" t="n"/>
+        <v>1902</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>2879</v>
+        <v>3850</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1293</v>
+        <v>1883</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 1 продаж</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>870</v>
+        <v>1302</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>0.3023063563737409</v>
+        <v>0.3382311688311688</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>2020</v>
+        <v>2700</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>1548</v>
+        <v>2053</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>2020</v>
+        <v>2720</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>1588</v>
-      </c>
-      <c r="N49" s="5" t="n"/>
+        <v>2125</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%; дубль с другой ценой: DQ500</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>191</v>
+        <v>50</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>2879</v>
+        <v>3850</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1293</v>
+        <v>1798</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
@@ -3056,22 +3173,22 @@
         </is>
       </c>
       <c r="H50" s="6" t="n">
-        <v>620</v>
+        <v>1217</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>0.2154706495310872</v>
+        <v>0.3161038961038961</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>2020</v>
+        <v>2700</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>1298</v>
+        <v>2053</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>2020</v>
+        <v>2720</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>1338</v>
+        <v>2125</v>
       </c>
       <c r="N50" s="5" t="n"/>
       <c r="O50" s="5" t="inlineStr">
@@ -3083,25 +3200,25 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>2860</v>
+        <v>3850</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1264</v>
+        <v>1823</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
@@ -3109,22 +3226,22 @@
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>942</v>
+        <v>1192</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>0.3295139860139861</v>
+        <v>0.3096103896103896</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>1630</v>
+        <v>2003</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>2000</v>
+        <v>2790</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>1670</v>
+        <v>2139</v>
       </c>
       <c r="N51" s="5" t="n"/>
       <c r="O51" s="5" t="inlineStr">
@@ -3136,25 +3253,25 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>180</v>
+        <v>400</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>2540</v>
+        <v>3850</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>1142</v>
+        <v>1823</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -3162,22 +3279,22 @@
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>809</v>
+        <v>1192</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>0.3186614173228347</v>
+        <v>0.3096103896103896</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>1780</v>
+        <v>2700</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>1404</v>
+        <v>2003</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>1780</v>
+        <v>2790</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>1440</v>
+        <v>2139</v>
       </c>
       <c r="N52" s="5" t="n"/>
       <c r="O52" s="5" t="inlineStr">
@@ -3189,50 +3306,52 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>2490</v>
+        <v>3350</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1116</v>
+        <v>979</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 20 продаж</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>866</v>
+        <v>528</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>0.3479518072289157</v>
+        <v>0.1576261194029851</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>1740</v>
+        <v>2350</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>1449</v>
+        <v>1841</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>1740</v>
+        <v>2440</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>1483</v>
-      </c>
-      <c r="N53" s="5" t="n"/>
+        <v>1970</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -3242,103 +3361,107 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>2450</v>
+        <v>2850</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1047</v>
+        <v>613</v>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 4 продаж</t>
         </is>
       </c>
       <c r="H54" s="6" t="n">
-        <v>895</v>
+        <v>42</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>0.3653061224489796</v>
+        <v>0.01476842105263159</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>1720</v>
+        <v>1990</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>1526</v>
+        <v>1371</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>1720</v>
+        <v>2020</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>1560</v>
-      </c>
-      <c r="N54" s="5" t="n"/>
+        <v>1438</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>1043</v>
+        <v>1266</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 8 продаж</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>702</v>
+        <v>595</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>0.2987234042553191</v>
+        <v>0.2086013157894737</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>1650</v>
+        <v>1990</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>1650</v>
+        <v>2020</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>1301</v>
-      </c>
-      <c r="N55" s="5" t="n"/>
+        <v>1338</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -3348,48 +3471,48 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="E56" s="6" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>1255</v>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>584</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>0.2049122807017544</v>
+      </c>
+      <c r="J56" s="6" t="n">
         <v>1990</v>
       </c>
-      <c r="F56" s="6" t="n">
-        <v>856</v>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>556</v>
-      </c>
-      <c r="I56" s="7" t="n">
-        <v>0.2795979899497487</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>1390</v>
-      </c>
       <c r="K56" s="6" t="n">
-        <v>1057</v>
+        <v>1271</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>1390</v>
+        <v>2020</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>1085</v>
+        <v>1338</v>
       </c>
       <c r="N56" s="5" t="n"/>
       <c r="O56" s="5" t="inlineStr">
@@ -3401,103 +3524,105 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E57" s="6" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>1178</v>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>407</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>0.1428070175438597</v>
+      </c>
+      <c r="J57" s="6" t="n">
         <v>1990</v>
       </c>
-      <c r="F57" s="6" t="n">
-        <v>856</v>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>636</v>
-      </c>
-      <c r="I57" s="7" t="n">
-        <v>0.3197989949748744</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>1390</v>
-      </c>
       <c r="K57" s="6" t="n">
-        <v>1137</v>
+        <v>1171</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>1390</v>
+        <v>1370</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>1165</v>
+        <v>647</v>
       </c>
       <c r="N57" s="5" t="n"/>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1950</v>
+        <v>2350</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>810</v>
+        <v>753</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 27 продаж</t>
         </is>
       </c>
       <c r="H58" s="6" t="n">
-        <v>343</v>
+        <v>432</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>0.1758974358974359</v>
+        <v>0.1838037825059101</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>1370</v>
+        <v>1650</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>869</v>
+        <v>1288</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>1370</v>
+        <v>1780</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>897</v>
-      </c>
-      <c r="N58" s="5" t="n"/>
+        <v>1440</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>27</v>
+      </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -3507,25 +3632,25 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1950</v>
+        <v>2350</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>835</v>
+        <v>995</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
@@ -3533,22 +3658,22 @@
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>518</v>
+        <v>849</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>0.2656410256410257</v>
+        <v>0.3612765957446809</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>1370</v>
+        <v>1650</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>1019</v>
+        <v>1463</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>1370</v>
+        <v>1720</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>1047</v>
+        <v>1560</v>
       </c>
       <c r="N59" s="5" t="n"/>
       <c r="O59" s="5" t="inlineStr">
@@ -3560,25 +3685,25 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1890</v>
+        <v>2350</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>804</v>
+        <v>1043</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
@@ -3586,22 +3711,22 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>440</v>
+        <v>702</v>
       </c>
       <c r="I60" s="7" t="n">
-        <v>0.2330158730158731</v>
+        <v>0.2987234042553191</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>1320</v>
+        <v>1650</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>925</v>
+        <v>1268</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>1320</v>
+        <v>1650</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>951</v>
+        <v>1301</v>
       </c>
       <c r="N60" s="5" t="n"/>
       <c r="O60" s="5" t="inlineStr">
@@ -3613,50 +3738,52 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>1880</v>
+        <v>2350</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>799</v>
+        <v>1028</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 2 продаж</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>586</v>
+        <v>787</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>0.3115957446808512</v>
+        <v>0.3346936170212766</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>1320</v>
+        <v>1650</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>1075</v>
+        <v>1368</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>1320</v>
+        <v>1740</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>1101</v>
-      </c>
-      <c r="N61" s="5" t="n"/>
+        <v>1483</v>
+      </c>
+      <c r="N61" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -3678,13 +3805,13 @@
         <v>76</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1879</v>
+        <v>1850</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
@@ -3692,77 +3819,79 @@
         </is>
       </c>
       <c r="H62" s="6" t="n">
-        <v>235</v>
+        <v>522</v>
       </c>
       <c r="I62" s="7" t="n">
-        <v>0.1252474720596062</v>
+        <v>0.2821621621621622</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>1320</v>
+        <v>1300</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>725</v>
+        <v>1007</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>1320</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>751</v>
+        <v>1051</v>
       </c>
       <c r="N62" s="5" t="n"/>
       <c r="O62" s="5" t="inlineStr">
         <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>1690</v>
+        <v>1850</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>700</v>
+        <v>927</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 1 продаж</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>548</v>
+        <v>636</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>0.3244970414201184</v>
+        <v>0.3435621621621622</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>1180</v>
+        <v>1300</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>1000</v>
+        <v>977</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>1180</v>
+        <v>1390</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>1024</v>
-      </c>
-      <c r="N63" s="5" t="n"/>
+        <v>1085</v>
+      </c>
+      <c r="N63" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -3772,50 +3901,52 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>1610</v>
+        <v>1850</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>658</v>
+        <v>717</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 15 продаж</t>
         </is>
       </c>
       <c r="H64" s="6" t="n">
-        <v>432</v>
+        <v>506</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>0.2680745341614907</v>
+        <v>0.2735077477477477</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>1130</v>
+        <v>1300</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>876</v>
+        <v>1057</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>1130</v>
+        <v>1390</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>898</v>
-      </c>
-      <c r="N64" s="5" t="n"/>
+        <v>1165</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -3825,103 +3956,107 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>1490</v>
+        <v>1850</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>596</v>
+        <v>332</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 8 продаж</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>256</v>
+        <v>121</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>0.1720805369127517</v>
+        <v>0.06560878378378379</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>1040</v>
+        <v>1300</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>676</v>
+        <v>1057</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>1040</v>
+        <v>1320</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>696</v>
-      </c>
-      <c r="N65" s="5" t="n"/>
+        <v>1101</v>
+      </c>
+      <c r="N65" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1490</v>
+        <v>1850</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>596</v>
+        <v>537</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 11 продаж</t>
         </is>
       </c>
       <c r="H66" s="6" t="n">
-        <v>386</v>
+        <v>296</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>0.2593288590604028</v>
+        <v>0.1602520884520885</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>1040</v>
+        <v>1300</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>806</v>
+        <v>1027</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>1040</v>
+        <v>1130</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>826</v>
-      </c>
-      <c r="N66" s="5" t="n"/>
+        <v>898</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -3931,50 +4066,52 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
+          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>1479</v>
+        <v>1850</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>590</v>
+        <v>851</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 5 продаж</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>0.237552400270453</v>
+        <v>0.2107372972972973</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>1040</v>
+        <v>1300</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>776</v>
+        <v>807</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>1040</v>
+        <v>1370</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>796</v>
-      </c>
-      <c r="N67" s="5" t="n"/>
+        <v>897</v>
+      </c>
+      <c r="N67" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -3984,25 +4121,25 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1479</v>
+        <v>1850</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>590</v>
+        <v>758</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
@@ -4010,22 +4147,22 @@
         </is>
       </c>
       <c r="H68" s="6" t="n">
-        <v>321</v>
+        <v>447</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>0.2172684246112238</v>
+        <v>0.2416216216216216</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>1040</v>
+        <v>1300</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>746</v>
+        <v>957</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>1040</v>
+        <v>690</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>766</v>
+        <v>428</v>
       </c>
       <c r="N68" s="5" t="n"/>
       <c r="O68" s="5" t="inlineStr">
@@ -4037,78 +4174,80 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1479</v>
+        <v>1850</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>590</v>
+        <v>506</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 9 продаж</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>301</v>
+        <v>115</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>0.2037457741717377</v>
+        <v>0.06202642642642642</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>1040</v>
+        <v>1300</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>726</v>
+        <v>877</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>1040</v>
+        <v>870</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>746</v>
-      </c>
-      <c r="N69" s="5" t="n"/>
+        <v>512</v>
+      </c>
+      <c r="N69" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1479</v>
+        <v>1850</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>590</v>
+        <v>783</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
@@ -4116,22 +4255,22 @@
         </is>
       </c>
       <c r="H70" s="6" t="n">
-        <v>401</v>
+        <v>622</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>0.2713590263691684</v>
+        <v>0.3362162162162162</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>1040</v>
+        <v>1300</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>826</v>
+        <v>1107</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>1040</v>
+        <v>1180</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>846</v>
+        <v>1024</v>
       </c>
       <c r="N70" s="5" t="n"/>
       <c r="O70" s="5" t="inlineStr">
@@ -4143,25 +4282,25 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>1380</v>
+        <v>1850</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>539</v>
+        <v>783</v>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
@@ -4169,22 +4308,22 @@
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>306</v>
+        <v>422</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>0.2215942028985508</v>
+        <v>0.2281081081081081</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>970</v>
+        <v>1300</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>713</v>
+        <v>907</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>970</v>
+        <v>1320</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>733</v>
+        <v>951</v>
       </c>
       <c r="N71" s="5" t="n"/>
       <c r="O71" s="5" t="inlineStr">
@@ -4196,25 +4335,25 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D72" s="6" t="n">
         <v>200</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>1290</v>
+        <v>1850</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>492</v>
+        <v>783</v>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
@@ -4222,24 +4361,26 @@
         </is>
       </c>
       <c r="H72" s="6" t="n">
-        <v>214</v>
+        <v>472</v>
       </c>
       <c r="I72" s="7" t="n">
-        <v>0.166201550387597</v>
+        <v>0.2551351351351351</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>601</v>
+        <v>957</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>900</v>
+        <v>1370</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>619</v>
-      </c>
-      <c r="N72" s="5" t="n"/>
+        <v>1047</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -4249,50 +4390,52 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>251</v>
+        <v>109</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1240</v>
+        <v>1350</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>466</v>
+        <v>526</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 7 продаж</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>0.2833870967741936</v>
+        <v>0.2185735449735449</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>870</v>
+        <v>940</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>734</v>
+        <v>687</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>870</v>
+        <v>1040</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>752</v>
-      </c>
-      <c r="N73" s="5" t="n"/>
+        <v>796</v>
+      </c>
+      <c r="N73" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -4302,290 +4445,300 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
-        <v>261</v>
+        <v>156</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1240</v>
+        <v>1350</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 7 продаж</t>
         </is>
       </c>
       <c r="H74" s="6" t="n">
-        <v>361</v>
+        <v>162</v>
       </c>
       <c r="I74" s="7" t="n">
-        <v>0.2914516129032259</v>
+        <v>0.1201280423280423</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>870</v>
+        <v>940</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>744</v>
+        <v>657</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>870</v>
+        <v>1040</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>762</v>
-      </c>
-      <c r="N74" s="5" t="n"/>
+        <v>766</v>
+      </c>
+      <c r="N74" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>1240</v>
+        <v>1350</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>418</v>
+        <v>658</v>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 28 продаж</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>63</v>
+        <v>327</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>0.05112903225806459</v>
+        <v>0.2425455026455026</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>870</v>
+        <v>940</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>494</v>
+        <v>587</v>
       </c>
       <c r="L75" s="6" t="n">
-        <v>870</v>
+        <v>1040</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>512</v>
-      </c>
-      <c r="N75" s="5" t="n"/>
+        <v>696</v>
+      </c>
+      <c r="N75" s="5" t="n">
+        <v>28</v>
+      </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>107</v>
+        <v>251</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>999</v>
+        <v>1350</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>340</v>
+        <v>131</v>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 6 продаж</t>
         </is>
       </c>
       <c r="H76" s="6" t="n">
-        <v>221</v>
+        <v>10</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>0.2207607607607608</v>
+        <v>0.007271604938271602</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>700</v>
+        <v>940</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>563</v>
+        <v>797</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>500</v>
+        <v>870</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>395</v>
-      </c>
-      <c r="N76" s="5" t="n"/>
+        <v>752</v>
+      </c>
+      <c r="N76" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>999</v>
+        <v>1350</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 25 продаж</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>211</v>
+        <v>92</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>0.2107507507507508</v>
+        <v>0.06831525925925924</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>700</v>
+        <v>940</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>553</v>
+        <v>637</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>700</v>
+        <v>1040</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>567</v>
-      </c>
-      <c r="N77" s="5" t="n"/>
+        <v>746</v>
+      </c>
+      <c r="N77" s="5" t="n">
+        <v>25</v>
+      </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
-        <v>13</v>
+        <v>261</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>999</v>
+        <v>1350</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>340</v>
+        <v>419</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 10 продаж</t>
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>131</v>
+        <v>308</v>
       </c>
       <c r="I78" s="7" t="n">
-        <v>0.1306706706706707</v>
+        <v>0.2278296296296296</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>700</v>
+        <v>940</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>473</v>
+        <v>807</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>700</v>
+        <v>870</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>487</v>
-      </c>
-      <c r="N78" s="5" t="n"/>
+        <v>762</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="O78" s="5" t="inlineStr">
         <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>999</v>
+        <v>1350</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>340</v>
+        <v>523</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
@@ -4593,105 +4746,107 @@
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>31</v>
+        <v>322</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>0.03057057057057059</v>
+        <v>0.2385185185185185</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>700</v>
+        <v>940</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>373</v>
+        <v>717</v>
       </c>
       <c r="L79" s="6" t="n">
-        <v>700</v>
+        <v>1040</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>387</v>
+        <v>826</v>
       </c>
       <c r="N79" s="5" t="n"/>
       <c r="O79" s="5" t="inlineStr">
         <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>999</v>
+        <v>1350</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>340</v>
+        <v>563</v>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 1 продаж</t>
         </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>31</v>
+        <v>332</v>
       </c>
       <c r="I80" s="7" t="n">
-        <v>0.03057057057057059</v>
+        <v>0.2458814814814815</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>700</v>
+        <v>940</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>373</v>
+        <v>687</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>387</v>
-      </c>
-      <c r="N80" s="5" t="n"/>
+        <v>669</v>
+      </c>
+      <c r="N80" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O80" s="5" t="inlineStr">
         <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>999</v>
+        <v>1350</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>340</v>
+        <v>523</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
@@ -4699,52 +4854,52 @@
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>31</v>
+        <v>292</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>0.03057057057057059</v>
+        <v>0.2162962962962963</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>700</v>
+        <v>940</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>373</v>
+        <v>687</v>
       </c>
       <c r="L81" s="6" t="n">
-        <v>700</v>
+        <v>970</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>387</v>
+        <v>733</v>
       </c>
       <c r="N81" s="5" t="n"/>
       <c r="O81" s="5" t="inlineStr">
         <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>999</v>
+        <v>1350</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>340</v>
+        <v>523</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
@@ -4752,87 +4907,105 @@
         </is>
       </c>
       <c r="H82" s="6" t="n">
-        <v>31</v>
+        <v>322</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>0.03057057057057059</v>
+        <v>0.2385185185185185</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>700</v>
+        <v>940</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>373</v>
+        <v>717</v>
       </c>
       <c r="L82" s="6" t="n">
-        <v>700</v>
+        <v>1040</v>
       </c>
       <c r="M82" s="6" t="n">
-        <v>387</v>
+        <v>826</v>
       </c>
       <c r="N82" s="5" t="n"/>
       <c r="O82" s="5" t="inlineStr">
         <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="6" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>120</v>
+      </c>
       <c r="E83" s="6" t="n">
-        <v>990</v>
-      </c>
-      <c r="F83" s="6" t="n"/>
-      <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="6" t="n"/>
-      <c r="I83" s="7" t="n"/>
-      <c r="J83" s="6" t="n"/>
-      <c r="K83" s="6" t="n"/>
+        <v>1350</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>523</v>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>322</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>0.2385185185185185</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>940</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>717</v>
+      </c>
       <c r="L83" s="6" t="n">
-        <v>690</v>
-      </c>
-      <c r="M83" s="6" t="n"/>
+        <v>1040</v>
+      </c>
+      <c r="M83" s="6" t="n">
+        <v>826</v>
+      </c>
       <c r="N83" s="5" t="n"/>
       <c r="O83" s="5" t="inlineStr">
         <is>
-          <t>нет закупки</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>990</v>
+        <v>1350</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>311</v>
+        <v>523</v>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
@@ -4840,22 +5013,22 @@
         </is>
       </c>
       <c r="H84" s="6" t="n">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="I84" s="7" t="n">
-        <v>0.05191919191919198</v>
+        <v>0.1422222222222222</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>690</v>
+        <v>940</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>414</v>
+        <v>587</v>
       </c>
       <c r="L84" s="6" t="n">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="M84" s="6" t="n">
-        <v>428</v>
+        <v>387</v>
       </c>
       <c r="N84" s="5" t="n"/>
       <c r="O84" s="5" t="inlineStr">
@@ -4867,25 +5040,25 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>980</v>
+        <v>1350</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>331</v>
+        <v>523</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
@@ -4893,22 +5066,22 @@
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>122</v>
+        <v>192</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>0.1242857142857142</v>
+        <v>0.1422222222222222</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>690</v>
+        <v>940</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>464</v>
+        <v>587</v>
       </c>
       <c r="L85" s="6" t="n">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="M85" s="6" t="n">
-        <v>478</v>
+        <v>387</v>
       </c>
       <c r="N85" s="5" t="n"/>
       <c r="O85" s="5" t="inlineStr">
@@ -4920,25 +5093,25 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>979</v>
+        <v>1350</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>330</v>
+        <v>523</v>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
@@ -4946,52 +5119,52 @@
         </is>
       </c>
       <c r="H86" s="6" t="n">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="I86" s="7" t="n">
-        <v>0.2363023493360572</v>
+        <v>0.1422222222222222</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>690</v>
+        <v>940</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="L86" s="6" t="n">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="M86" s="6" t="n">
-        <v>588</v>
+        <v>387</v>
       </c>
       <c r="N86" s="5" t="n"/>
       <c r="O86" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>979</v>
+        <v>1350</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>330</v>
+        <v>523</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
@@ -4999,52 +5172,52 @@
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>0.2107660878447395</v>
+        <v>0.1422222222222222</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>690</v>
+        <v>940</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>549</v>
+        <v>587</v>
       </c>
       <c r="L87" s="6" t="n">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="M87" s="6" t="n">
-        <v>563</v>
+        <v>387</v>
       </c>
       <c r="N87" s="5" t="n"/>
       <c r="O87" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>979</v>
+        <v>950</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
@@ -5052,22 +5225,22 @@
         </is>
       </c>
       <c r="H88" s="6" t="n">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>0.1750153217568948</v>
+        <v>0.208421052631579</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>690</v>
+        <v>500</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>528</v>
+        <v>395</v>
       </c>
       <c r="N88" s="5" t="n"/>
       <c r="O88" s="5" t="inlineStr">
@@ -5079,25 +5252,25 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>979</v>
+        <v>950</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
@@ -5105,22 +5278,22 @@
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>251</v>
+        <v>188</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>0.2567313585291113</v>
+        <v>0.1978947368421053</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>594</v>
+        <v>526</v>
       </c>
       <c r="L89" s="6" t="n">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="M89" s="6" t="n">
-        <v>608</v>
+        <v>567</v>
       </c>
       <c r="N89" s="5" t="n"/>
       <c r="O89" s="5" t="inlineStr">
@@ -5132,50 +5305,52 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>979</v>
+        <v>950</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>330</v>
+        <v>408</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 2 продаж</t>
         </is>
       </c>
       <c r="H90" s="6" t="n">
-        <v>176</v>
+        <v>311</v>
       </c>
       <c r="I90" s="7" t="n">
-        <v>0.1801225740551583</v>
+        <v>0.3277473684210526</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>690</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>533</v>
-      </c>
-      <c r="N90" s="5" t="n"/>
+        <v>588</v>
+      </c>
+      <c r="N90" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="O90" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -5185,50 +5360,52 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E91" s="6" t="n">
         <v>950</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>315</v>
+        <v>368</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 7 продаж</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>0.2452631578947368</v>
+        <v>0.2585172932330826</v>
       </c>
       <c r="J91" s="6" t="n">
         <v>670</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>571</v>
+        <v>531</v>
       </c>
       <c r="L91" s="6" t="n">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>585</v>
-      </c>
-      <c r="N91" s="5" t="n"/>
+        <v>563</v>
+      </c>
+      <c r="N91" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="O91" s="5" t="inlineStr">
         <is>
           <t>прибыль Ozon/Авито отличается &gt;30%</t>
@@ -5253,27 +5430,27 @@
         <v>150</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>931</v>
+        <v>950</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>305</v>
+        <v>247</v>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 7 продаж</t>
         </is>
       </c>
       <c r="H92" s="6" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="I92" s="7" t="n">
-        <v>0.1066165413533834</v>
+        <v>0.0416075187969925</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>650</v>
@@ -5281,7 +5458,9 @@
       <c r="M92" s="6" t="n">
         <v>442</v>
       </c>
-      <c r="N92" s="5" t="n"/>
+      <c r="N92" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="O92" s="5" t="inlineStr">
         <is>
           <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
@@ -5291,78 +5470,80 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X301127C</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>206</v>
+        <v>122</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>879</v>
+        <v>950</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>278</v>
+        <v>383</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 32 продаж</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>130</v>
+        <v>226</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>0.1482821387940842</v>
+        <v>0.2378697368421052</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="L93" s="6" t="n">
-        <v>620</v>
+        <v>690</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>469</v>
-      </c>
-      <c r="N93" s="5" t="n"/>
+        <v>528</v>
+      </c>
+      <c r="N93" s="5" t="n">
+        <v>32</v>
+      </c>
       <c r="O93" s="5" t="inlineStr">
         <is>
-          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>263</v>
+        <v>315</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
@@ -5370,52 +5551,52 @@
         </is>
       </c>
       <c r="H94" s="6" t="n">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="I94" s="7" t="n">
-        <v>0.2141176470588235</v>
+        <v>0.1136842105263158</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>504</v>
+        <v>446</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="N94" s="5" t="n"/>
       <c r="O94" s="5" t="inlineStr">
         <is>
-          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>2 кольца-прокладки на 1 втулку мехатроника DSG7 DQ200</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>840</v>
+        <v>950</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>258</v>
+        <v>315</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
@@ -5423,22 +5604,22 @@
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>157</v>
+        <v>238</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>0.1873809523809525</v>
+        <v>0.2505263157894737</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>590</v>
+        <v>670</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>475</v>
+        <v>576</v>
       </c>
       <c r="L95" s="6" t="n">
-        <v>590</v>
+        <v>690</v>
       </c>
       <c r="M95" s="6" t="n">
-        <v>487</v>
+        <v>608</v>
       </c>
       <c r="N95" s="5" t="n"/>
       <c r="O95" s="5" t="inlineStr">
@@ -5450,254 +5631,264 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
+          <t>filtr-dsg7-dq200</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>343</v>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>факт: 3 продаж</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <v>0.1431719298245614</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>670</v>
+      </c>
+      <c r="K96" s="6" t="n">
+        <v>446</v>
+      </c>
+      <c r="L96" s="6" t="n">
+        <v>690</v>
+      </c>
+      <c r="M96" s="6" t="n">
+        <v>478</v>
+      </c>
+      <c r="N96" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O96" s="5" t="inlineStr">
+        <is>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>klipsy-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>315</v>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>233</v>
+      </c>
+      <c r="I97" s="7" t="n">
+        <v>0.2452631578947368</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>670</v>
+      </c>
+      <c r="K97" s="6" t="n">
+        <v>571</v>
+      </c>
+      <c r="L97" s="6" t="n">
+        <v>670</v>
+      </c>
+      <c r="M97" s="6" t="n">
+        <v>585</v>
+      </c>
+      <c r="N97" s="5" t="n"/>
+      <c r="O97" s="5" t="inlineStr">
+        <is>
+          <t>прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>nakladki-pedali</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="F98" s="6" t="n"/>
+      <c r="G98" s="5" t="inlineStr"/>
+      <c r="H98" s="6" t="n"/>
+      <c r="I98" s="7" t="n"/>
+      <c r="J98" s="6" t="n"/>
+      <c r="K98" s="6" t="n"/>
+      <c r="L98" s="6" t="n">
+        <v>690</v>
+      </c>
+      <c r="M98" s="6" t="n"/>
+      <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="inlineStr">
+        <is>
+          <t>нет закупки</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>plastina-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>факт: 1 продаж</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="I99" s="7" t="n">
+        <v>0.02429473684210528</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>670</v>
+      </c>
+      <c r="K99" s="6" t="n">
+        <v>516</v>
+      </c>
+      <c r="L99" s="6" t="n">
+        <v>340</v>
+      </c>
+      <c r="M99" s="6" t="n">
+        <v>229</v>
+      </c>
+      <c r="N99" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" s="5" t="inlineStr">
+        <is>
+          <t>низкая маржа Ozon; прибыль Ozon/Авито отличается &gt;30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
           <t>TEST001</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>Тестовый товар не публикуется</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="6" t="n">
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="F96" s="6" t="n">
+      <c r="F100" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>оценка по тарифам</t>
         </is>
       </c>
-      <c r="H96" s="6" t="n"/>
-      <c r="I96" s="7" t="n"/>
-      <c r="J96" s="6" t="n"/>
-      <c r="K96" s="6" t="n"/>
-      <c r="L96" s="6" t="n">
+      <c r="H100" s="6" t="n"/>
+      <c r="I100" s="7" t="n"/>
+      <c r="J100" s="6" t="n"/>
+      <c r="K100" s="6" t="n"/>
+      <c r="L100" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="M96" s="6" t="n"/>
-      <c r="N96" s="5" t="n"/>
-      <c r="O96" s="5" t="inlineStr">
+      <c r="M100" s="6" t="n"/>
+      <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="inlineStr">
         <is>
           <t>нет закупки</t>
         </is>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>0am325025HX</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769D</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D97" s="9" t="n">
-        <v>31000</v>
-      </c>
-      <c r="E97" s="9" t="n">
-        <v>128800</v>
-      </c>
-      <c r="F97" s="9" t="n">
-        <v>65858</v>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="n">
-        <v>27130</v>
-      </c>
-      <c r="I97" s="10" t="n">
-        <v>0.2106366459627329</v>
-      </c>
-      <c r="J97" s="9" t="n">
-        <v>77280</v>
-      </c>
-      <c r="K97" s="9" t="n">
-        <v>37779</v>
-      </c>
-      <c r="L97" s="9" t="n">
-        <v>77280</v>
-      </c>
-      <c r="M97" s="9" t="n">
-        <v>39325</v>
-      </c>
-      <c r="N97" s="8" t="n"/>
-      <c r="O97" s="8" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>0AM927769D</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D98" s="9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="E98" s="9" t="n">
-        <v>78800</v>
-      </c>
-      <c r="F98" s="9" t="n">
-        <v>40037</v>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H98" s="9" t="n">
-        <v>17309</v>
-      </c>
-      <c r="I98" s="10" t="n">
-        <v>0.2196573604060914</v>
-      </c>
-      <c r="J98" s="9" t="n">
-        <v>47280</v>
-      </c>
-      <c r="K98" s="9" t="n">
-        <v>24079</v>
-      </c>
-      <c r="L98" s="9" t="n">
-        <v>47280</v>
-      </c>
-      <c r="M98" s="9" t="n">
-        <v>25025</v>
-      </c>
-      <c r="N98" s="8" t="n"/>
-      <c r="O98" s="8" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E99" s="9" t="n">
-        <v>58900</v>
-      </c>
-      <c r="F99" s="9" t="n">
-        <v>27914</v>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="n">
-        <v>14380</v>
-      </c>
-      <c r="I99" s="10" t="n">
-        <v>0.2441426146010187</v>
-      </c>
-      <c r="J99" s="9" t="n"/>
-      <c r="K99" s="9" t="n"/>
-      <c r="L99" s="9" t="n">
-        <v>35340</v>
-      </c>
-      <c r="M99" s="9" t="n">
-        <v>22159</v>
-      </c>
-      <c r="N99" s="8" t="n"/>
-      <c r="O99" s="8" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E100" s="9" t="n">
-        <v>58900</v>
-      </c>
-      <c r="F100" s="9" t="n">
-        <v>27914</v>
-      </c>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H100" s="9" t="n">
-        <v>14380</v>
-      </c>
-      <c r="I100" s="10" t="n">
-        <v>0.2441426146010187</v>
-      </c>
-      <c r="J100" s="9" t="n"/>
-      <c r="K100" s="9" t="n"/>
-      <c r="L100" s="9" t="n">
-        <v>35340</v>
-      </c>
-      <c r="M100" s="9" t="n">
-        <v>22159</v>
-      </c>
-      <c r="N100" s="8" t="n"/>
-      <c r="O100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>16890</v>
+        <v>58850</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>8543</v>
+        <v>27888</v>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
@@ -5705,18 +5896,18 @@
         </is>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5029</v>
+        <v>14357</v>
       </c>
       <c r="I101" s="10" t="n">
-        <v>0.297773830669035</v>
+        <v>0.2439592183517417</v>
       </c>
       <c r="J101" s="9" t="n"/>
       <c r="K101" s="9" t="n"/>
       <c r="L101" s="9" t="n">
-        <v>11820</v>
+        <v>35340</v>
       </c>
       <c r="M101" s="9" t="n">
-        <v>8256</v>
+        <v>22159</v>
       </c>
       <c r="N101" s="8" t="n"/>
       <c r="O101" s="8" t="inlineStr"/>
@@ -5724,25 +5915,25 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>12979</v>
+        <v>58850</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>6570</v>
+        <v>27888</v>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
@@ -5750,18 +5941,18 @@
         </is>
       </c>
       <c r="H102" s="9" t="n">
-        <v>4291</v>
+        <v>14357</v>
       </c>
       <c r="I102" s="10" t="n">
-        <v>0.3306371831419987</v>
+        <v>0.2439592183517417</v>
       </c>
       <c r="J102" s="9" t="n"/>
       <c r="K102" s="9" t="n"/>
       <c r="L102" s="9" t="n">
-        <v>9090</v>
+        <v>35340</v>
       </c>
       <c r="M102" s="9" t="n">
-        <v>6772</v>
+        <v>22159</v>
       </c>
       <c r="N102" s="8" t="n"/>
       <c r="O102" s="8" t="inlineStr"/>
@@ -5769,70 +5960,72 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>11979</v>
+        <v>19850</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>6002</v>
+        <v>9793</v>
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>оценка по тарифам</t>
+          <t>факт: 4 продаж</t>
         </is>
       </c>
       <c r="H103" s="9" t="n">
-        <v>2283</v>
+        <v>5102</v>
       </c>
       <c r="I103" s="10" t="n">
-        <v>0.1906119041656232</v>
+        <v>0.2570256926952141</v>
       </c>
       <c r="J103" s="9" t="n"/>
       <c r="K103" s="9" t="n"/>
       <c r="L103" s="9" t="n">
-        <v>8390</v>
+        <v>13860</v>
       </c>
       <c r="M103" s="9" t="n">
-        <v>4635</v>
-      </c>
-      <c r="N103" s="8" t="n"/>
+        <v>9113</v>
+      </c>
+      <c r="N103" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="O103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>11979</v>
+        <v>16850</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>6002</v>
+        <v>8522</v>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
@@ -5840,18 +6033,18 @@
         </is>
       </c>
       <c r="H104" s="9" t="n">
-        <v>3483</v>
+        <v>5011</v>
       </c>
       <c r="I104" s="10" t="n">
-        <v>0.2907872109525002</v>
+        <v>0.2973887240356083</v>
       </c>
       <c r="J104" s="9" t="n"/>
       <c r="K104" s="9" t="n"/>
       <c r="L104" s="9" t="n">
-        <v>8390</v>
+        <v>11820</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>5835</v>
+        <v>8256</v>
       </c>
       <c r="N104" s="8" t="n"/>
       <c r="O104" s="8" t="inlineStr"/>
@@ -5859,34 +6052,44 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F105" s="9" t="n"/>
-      <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="10" t="n"/>
+        <v>12850</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>6503</v>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>4232</v>
+      </c>
+      <c r="I105" s="10" t="n">
+        <v>0.3293385214007782</v>
+      </c>
       <c r="J105" s="9" t="n"/>
       <c r="K105" s="9" t="n"/>
       <c r="L105" s="9" t="n">
-        <v>6650</v>
+        <v>9090</v>
       </c>
       <c r="M105" s="9" t="n">
-        <v>3851</v>
+        <v>6772</v>
       </c>
       <c r="N105" s="8" t="n"/>
       <c r="O105" s="8" t="inlineStr"/>
@@ -5894,34 +6097,44 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
         </is>
       </c>
       <c r="C106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>2100</v>
+        <v>3000</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F106" s="9" t="n"/>
-      <c r="G106" s="8" t="inlineStr"/>
-      <c r="H106" s="9" t="n"/>
-      <c r="I106" s="10" t="n"/>
+        <v>11850</v>
+      </c>
+      <c r="F106" s="9" t="n">
+        <v>5935</v>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>2224</v>
+      </c>
+      <c r="I106" s="10" t="n">
+        <v>0.1876793248945148</v>
+      </c>
       <c r="J106" s="9" t="n"/>
       <c r="K106" s="9" t="n"/>
       <c r="L106" s="9" t="n">
-        <v>6650</v>
+        <v>8390</v>
       </c>
       <c r="M106" s="9" t="n">
-        <v>3951</v>
+        <v>4635</v>
       </c>
       <c r="N106" s="8" t="n"/>
       <c r="O106" s="8" t="inlineStr"/>
@@ -5929,34 +6142,44 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F107" s="9" t="n"/>
-      <c r="G107" s="8" t="inlineStr"/>
-      <c r="H107" s="9" t="n"/>
-      <c r="I107" s="10" t="n"/>
+        <v>11850</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>5935</v>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>3424</v>
+      </c>
+      <c r="I107" s="10" t="n">
+        <v>0.2889451476793249</v>
+      </c>
       <c r="J107" s="9" t="n"/>
       <c r="K107" s="9" t="n"/>
       <c r="L107" s="9" t="n">
-        <v>6650</v>
+        <v>8390</v>
       </c>
       <c r="M107" s="9" t="n">
-        <v>3951</v>
+        <v>5835</v>
       </c>
       <c r="N107" s="8" t="n"/>
       <c r="O107" s="8" t="inlineStr"/>
@@ -5964,44 +6187,34 @@
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>8890</v>
-      </c>
-      <c r="F108" s="9" t="n">
-        <v>4396</v>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H108" s="9" t="n">
-        <v>2962</v>
-      </c>
-      <c r="I108" s="10" t="n">
-        <v>0.3332283464566929</v>
-      </c>
+        <v>9850</v>
+      </c>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="8" t="inlineStr"/>
+      <c r="H108" s="9" t="n"/>
+      <c r="I108" s="10" t="n"/>
       <c r="J108" s="9" t="n"/>
       <c r="K108" s="9" t="n"/>
       <c r="L108" s="9" t="n">
-        <v>6220</v>
+        <v>6650</v>
       </c>
       <c r="M108" s="9" t="n">
-        <v>4760</v>
+        <v>3851</v>
       </c>
       <c r="N108" s="8" t="n"/>
       <c r="O108" s="8" t="inlineStr"/>
@@ -6009,25 +6222,25 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>700</v>
+        <v>2100</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>6690</v>
+        <v>9850</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>3275</v>
+        <v>4818</v>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
@@ -6035,18 +6248,18 @@
         </is>
       </c>
       <c r="H109" s="9" t="n">
-        <v>2173</v>
+        <v>2127</v>
       </c>
       <c r="I109" s="10" t="n">
-        <v>0.3248729446935725</v>
+        <v>0.2159390862944162</v>
       </c>
       <c r="J109" s="9" t="n"/>
       <c r="K109" s="9" t="n"/>
       <c r="L109" s="9" t="n">
-        <v>1660</v>
+        <v>6650</v>
       </c>
       <c r="M109" s="9" t="n">
-        <v>811</v>
+        <v>3951</v>
       </c>
       <c r="N109" s="8" t="n"/>
       <c r="O109" s="8" t="inlineStr"/>
@@ -6054,25 +6267,25 @@
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>600</v>
+        <v>2100</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>4741</v>
+        <v>9850</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>2225</v>
+        <v>4818</v>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
@@ -6080,18 +6293,18 @@
         </is>
       </c>
       <c r="H110" s="9" t="n">
-        <v>1341</v>
+        <v>2127</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>0.2828221894115166</v>
+        <v>0.2159390862944162</v>
       </c>
       <c r="J110" s="9" t="n"/>
       <c r="K110" s="9" t="n"/>
       <c r="L110" s="9" t="n">
-        <v>3320</v>
+        <v>6650</v>
       </c>
       <c r="M110" s="9" t="n">
-        <v>2421</v>
+        <v>3951</v>
       </c>
       <c r="N110" s="8" t="n"/>
       <c r="O110" s="8" t="inlineStr"/>
@@ -6099,77 +6312,91 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>3990</v>
-      </c>
-      <c r="F111" s="9" t="n"/>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="9" t="n"/>
-      <c r="I111" s="10" t="n"/>
-      <c r="J111" s="9" t="n">
-        <v>2790</v>
-      </c>
-      <c r="K111" s="9" t="n">
-        <v>2083</v>
-      </c>
+        <v>8850</v>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>3752</v>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>факт: 1 продаж</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>2321</v>
+      </c>
+      <c r="I111" s="10" t="n">
+        <v>0.2622949152542373</v>
+      </c>
+      <c r="J111" s="9" t="n"/>
+      <c r="K111" s="9" t="n"/>
       <c r="L111" s="9" t="n">
-        <v>2790</v>
+        <v>6220</v>
       </c>
       <c r="M111" s="9" t="n">
-        <v>2139</v>
-      </c>
-      <c r="N111" s="8" t="n"/>
+        <v>4760</v>
+      </c>
+      <c r="N111" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="O111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>400</v>
+        <v>2100</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>3990</v>
-      </c>
-      <c r="F112" s="9" t="n"/>
-      <c r="G112" s="8" t="inlineStr"/>
-      <c r="H112" s="9" t="n"/>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="9" t="n">
-        <v>2790</v>
-      </c>
-      <c r="K112" s="9" t="n">
-        <v>2083</v>
-      </c>
+        <v>8850</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>4298</v>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="n">
+        <v>1667</v>
+      </c>
+      <c r="I112" s="10" t="n">
+        <v>0.188361581920904</v>
+      </c>
+      <c r="J112" s="9" t="n"/>
+      <c r="K112" s="9" t="n"/>
       <c r="L112" s="9" t="n">
-        <v>2790</v>
+        <v>5950</v>
       </c>
       <c r="M112" s="9" t="n">
-        <v>2139</v>
+        <v>3314</v>
       </c>
       <c r="N112" s="8" t="n"/>
       <c r="O112" s="8" t="inlineStr"/>
@@ -6177,25 +6404,25 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>2980</v>
+        <v>6850</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>1371</v>
+        <v>3358</v>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
@@ -6203,63 +6430,55 @@
         </is>
       </c>
       <c r="H113" s="9" t="n">
-        <v>1042</v>
+        <v>2247</v>
       </c>
       <c r="I113" s="10" t="n">
-        <v>0.3495973154362417</v>
+        <v>0.328029197080292</v>
       </c>
       <c r="J113" s="9" t="n"/>
       <c r="K113" s="9" t="n"/>
       <c r="L113" s="9" t="n">
-        <v>2090</v>
+        <v>1660</v>
       </c>
       <c r="M113" s="9" t="n">
-        <v>1752</v>
-      </c>
-      <c r="N113" s="8" t="n"/>
+        <v>811</v>
+      </c>
+      <c r="N113" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="O113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>2980</v>
-      </c>
-      <c r="F114" s="9" t="n">
-        <v>1371</v>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="n">
-        <v>1042</v>
-      </c>
-      <c r="I114" s="10" t="n">
-        <v>0.3495973154362417</v>
-      </c>
+        <v>3850</v>
+      </c>
+      <c r="F114" s="9" t="n"/>
+      <c r="G114" s="8" t="inlineStr"/>
+      <c r="H114" s="9" t="n"/>
+      <c r="I114" s="10" t="n"/>
       <c r="J114" s="9" t="n"/>
       <c r="K114" s="9" t="n"/>
       <c r="L114" s="9" t="n">
-        <v>2090</v>
+        <v>2720</v>
       </c>
       <c r="M114" s="9" t="n">
-        <v>1752</v>
+        <v>2125</v>
       </c>
       <c r="N114" s="8" t="n"/>
       <c r="O114" s="8" t="inlineStr"/>
@@ -6267,34 +6486,44 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="E115" s="9" t="n">
         <v>2850</v>
       </c>
-      <c r="F115" s="9" t="n"/>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="9" t="n"/>
-      <c r="I115" s="10" t="n"/>
+      <c r="F115" s="9" t="n">
+        <v>1303</v>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>оценка по тарифам</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="n">
+        <v>982</v>
+      </c>
+      <c r="I115" s="10" t="n">
+        <v>0.344561403508772</v>
+      </c>
       <c r="J115" s="9" t="n"/>
       <c r="K115" s="9" t="n"/>
       <c r="L115" s="9" t="n">
-        <v>1990</v>
+        <v>2090</v>
       </c>
       <c r="M115" s="9" t="n">
-        <v>1311</v>
+        <v>1752</v>
       </c>
       <c r="N115" s="8" t="n"/>
       <c r="O115" s="8" t="inlineStr"/>
@@ -6302,79 +6531,81 @@
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="E116" s="9" t="n">
         <v>2850</v>
       </c>
-      <c r="F116" s="9" t="n"/>
-      <c r="G116" s="8" t="inlineStr"/>
-      <c r="H116" s="9" t="n"/>
-      <c r="I116" s="10" t="n"/>
+      <c r="F116" s="9" t="n">
+        <v>835</v>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>факт: 4 продаж</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="n">
+        <v>514</v>
+      </c>
+      <c r="I116" s="10" t="n">
+        <v>0.1804578947368421</v>
+      </c>
       <c r="J116" s="9" t="n"/>
       <c r="K116" s="9" t="n"/>
       <c r="L116" s="9" t="n">
-        <v>1990</v>
+        <v>2090</v>
       </c>
       <c r="M116" s="9" t="n">
-        <v>1311</v>
-      </c>
-      <c r="N116" s="8" t="n"/>
+        <v>1752</v>
+      </c>
+      <c r="N116" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="O116" s="8" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>Обратный клапан масляного фильтра EA888 Gen3 06L115678AD для двигателей 1.8 2.0 TSI</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>2366</v>
-      </c>
-      <c r="F117" s="9" t="n">
-        <v>983</v>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>оценка по тарифам</t>
-        </is>
-      </c>
-      <c r="H117" s="9" t="n">
-        <v>691</v>
-      </c>
-      <c r="I117" s="10" t="n">
-        <v>0.2921048182586644</v>
-      </c>
+        <v>2850</v>
+      </c>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="9" t="n"/>
+      <c r="I117" s="10" t="n"/>
       <c r="J117" s="9" t="n"/>
       <c r="K117" s="9" t="n"/>
       <c r="L117" s="9" t="n">
-        <v>1660</v>
+        <v>1990</v>
       </c>
       <c r="M117" s="9" t="n">
-        <v>1361</v>
+        <v>1311</v>
       </c>
       <c r="N117" s="8" t="n"/>
       <c r="O117" s="8" t="inlineStr"/>
@@ -6382,38 +6613,34 @@
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
         </is>
       </c>
       <c r="C118" s="8" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>1870</v>
+        <v>2850</v>
       </c>
       <c r="F118" s="9" t="n"/>
       <c r="G118" s="8" t="inlineStr"/>
       <c r="H118" s="9" t="n"/>
       <c r="I118" s="10" t="n"/>
-      <c r="J118" s="9" t="n">
-        <v>1310</v>
-      </c>
-      <c r="K118" s="9" t="n">
-        <v>966</v>
-      </c>
+      <c r="J118" s="9" t="n"/>
+      <c r="K118" s="9" t="n"/>
       <c r="L118" s="9" t="n">
-        <v>1310</v>
+        <v>1990</v>
       </c>
       <c r="M118" s="9" t="n">
-        <v>992</v>
+        <v>1311</v>
       </c>
       <c r="N118" s="8" t="n"/>
       <c r="O118" s="8" t="inlineStr"/>
@@ -6421,25 +6648,25 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
+          <t>Обратный клапан масляного фильтра EA888 Gen3 06L115678AD для двигателей 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>1620</v>
+        <v>2350</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>663</v>
+        <v>973</v>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
@@ -6447,57 +6674,59 @@
         </is>
       </c>
       <c r="H119" s="9" t="n">
-        <v>476</v>
+        <v>682</v>
       </c>
       <c r="I119" s="10" t="n">
-        <v>0.2939506172839506</v>
+        <v>0.2902127659574468</v>
       </c>
       <c r="J119" s="9" t="n"/>
       <c r="K119" s="9" t="n"/>
       <c r="L119" s="9" t="n">
-        <v>1130</v>
+        <v>1660</v>
       </c>
       <c r="M119" s="9" t="n">
-        <v>938</v>
-      </c>
-      <c r="N119" s="8" t="n"/>
+        <v>1361</v>
+      </c>
+      <c r="N119" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="O119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C120" s="8" t="n">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>1490</v>
+        <v>2350</v>
       </c>
       <c r="F120" s="9" t="n"/>
       <c r="G120" s="8" t="inlineStr"/>
       <c r="H120" s="9" t="n"/>
       <c r="I120" s="10" t="n"/>
       <c r="J120" s="9" t="n">
-        <v>1040</v>
+        <v>1650</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>806</v>
+        <v>1268</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>1040</v>
+        <v>1310</v>
       </c>
       <c r="M120" s="9" t="n">
-        <v>826</v>
+        <v>992</v>
       </c>
       <c r="N120" s="8" t="n"/>
       <c r="O120" s="8" t="inlineStr"/>
@@ -6505,40 +6734,48 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>1490</v>
-      </c>
-      <c r="F121" s="9" t="n"/>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="9" t="n"/>
-      <c r="I121" s="10" t="n"/>
-      <c r="J121" s="9" t="n">
-        <v>1040</v>
-      </c>
-      <c r="K121" s="9" t="n">
-        <v>806</v>
-      </c>
+        <v>1850</v>
+      </c>
+      <c r="F121" s="9" t="n">
+        <v>570</v>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>факт: 9 продаж</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="n">
+        <v>369</v>
+      </c>
+      <c r="I121" s="10" t="n">
+        <v>0.1995423423423423</v>
+      </c>
+      <c r="J121" s="9" t="n"/>
+      <c r="K121" s="9" t="n"/>
       <c r="L121" s="9" t="n">
-        <v>1040</v>
+        <v>1130</v>
       </c>
       <c r="M121" s="9" t="n">
-        <v>826</v>
-      </c>
-      <c r="N121" s="8" t="n"/>
+        <v>938</v>
+      </c>
+      <c r="N121" s="8" t="n">
+        <v>9</v>
+      </c>
       <c r="O121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
@@ -6559,17 +6796,17 @@
         <v>100</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>980</v>
+        <v>1350</v>
       </c>
       <c r="F122" s="9" t="n"/>
       <c r="G122" s="8" t="inlineStr"/>
       <c r="H122" s="9" t="n"/>
       <c r="I122" s="10" t="n"/>
       <c r="J122" s="9" t="n">
-        <v>690</v>
+        <v>940</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>514</v>
+        <v>737</v>
       </c>
       <c r="L122" s="9" t="n">
         <v>690</v>
@@ -6598,17 +6835,17 @@
         <v>25</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="F123" s="9" t="n"/>
       <c r="G123" s="8" t="inlineStr"/>
       <c r="H123" s="9" t="n"/>
       <c r="I123" s="10" t="n"/>
       <c r="J123" s="9" t="n">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="L123" s="9" t="n">
         <v>410</v>
@@ -6637,17 +6874,17 @@
         <v>25</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="F124" s="9" t="n"/>
       <c r="G124" s="8" t="inlineStr"/>
       <c r="H124" s="9" t="n"/>
       <c r="I124" s="10" t="n"/>
       <c r="J124" s="9" t="n">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="L124" s="9" t="n">
         <v>410</v>
@@ -6729,7 +6966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -6738,15 +6975,375 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Период None..None</t>
+          <t>Период 2026-09-27..2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Гибкий график выплат</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>-41479</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Превышение индекса ошибок</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>-8611</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ускоренный сбор отзывов</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>-5185</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Страхование товара от массовых повреждений</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>-5127</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Отгрузка в нерекомендованный слот</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>-1224</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Жалобы покупателей</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Размещение товаров на складах Ozon</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>-66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Дополнительная упаковка на складе Ozon</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Упаковка товара партнёрами</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Обеспечение материалами для упаковки товара</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Товарная компенсация</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>5423</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Расхождение по многотоварным отправлениям</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>24453</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Все удержания и начисления по видам (для сверки с «Финансы» в кабинете)</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Вознаграждение за продажу</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>-1076402</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Логистика</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>-62040</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Гибкий график выплат</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>-41479</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Звёздные товары</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>-38215</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Подписка Управление отзывами</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>-31390</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Сбор первых отзывов</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>-28454</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Эквайринг</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>-20583</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Превышение индекса ошибок</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>-8611</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Обратная логистика</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>-7830</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ускоренный сбор отзывов</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>-5185</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Страхование товара от массовых повреждений</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>-5127</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Доставка до места выдачи</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>-4402</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Обработка отправления Drop-off партнёрами</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>-3030</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Доставка до места выдачи силами Ozon</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>-1250</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Отгрузка в нерекомендованный слот</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>-1224</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Обработка возвратов, отмен и невыкупов партнёрами</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>-555</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Продвижение бренда</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>-471</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Упаковка товара партнёрами</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>-270</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Обеспечение материалами для упаковки товара</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n">
+        <v>-135</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Временное размещение товара партнерами</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>-120</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Жалобы покупателей</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Размещение товаров на складах Ozon</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>-66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Дополнительная упаковка на складе Ozon</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Товарная компенсация</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>5423</v>
       </c>
     </row>
   </sheetData>
